--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:06:04+00:00</t>
+    <t>2025-03-11T13:09:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:09:22+00:00</t>
+    <t>2025-03-11T13:27:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:27:28+00:00</t>
+    <t>2025-03-11T13:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:28:38+00:00</t>
+    <t>2025-03-11T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -26,7 +26,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/ValueSet/CompromisedImmuneSystemCodes</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/ValueSet/CompromisedImmuneSystemCodes</t>
   </si>
   <si>
     <t>Version</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:29:42+00:00</t>
+    <t>2025-03-17T15:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-17T15:05:50+00:00</t>
+    <t>2025-03-18T10:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:04:30+00:00</t>
+    <t>2025-03-20T11:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T11:13:27+00:00</t>
+    <t>2025-03-20T15:00:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T15:00:12+00:00</t>
+    <t>2025-03-24T10:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:58:19+00:00</t>
+    <t>2025-03-24T11:01:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:08+00:00</t>
+    <t>2025-03-24T11:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:18+00:00</t>
+    <t>2025-03-24T12:21:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T12:21:29+00:00</t>
+    <t>2025-03-26T10:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-26T10:25:04+00:00</t>
+    <t>2025-04-06T05:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T05:59:28+00:00</t>
+    <t>2025-04-06T06:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T06:02:42+00:00</t>
+    <t>2025-04-10T08:21:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-10T08:21:04+00:00</t>
+    <t>2025-04-15T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>Property</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-15T15:53:54+00:00</t>
+    <t>2025-04-16T11:48:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,6 +90,11 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>*   This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement
+*   The SNOMED International IPS Terminology is distributed by International Health Terminology Standards Development Organisation, trading as SNOMED International, and is subject the terms of the [Creative Commons Attribution 4.0 International Public License](https://creativecommons.org/licenses/by/4.0/). For more information, see [SNOMED IPS Terminology](https://www.snomed.org/snomed-ct/Other-SNOMED-products/international-patient-summary-terminology)
+*   The HL7 International IPS implementation guides incorporate SNOMED CT®, used by permission of the International Health Terminology Standards Development Organisation, trading as SNOMED International. SNOMED CT was originally created by the College of American Pathologists. SNOMED CT is a registered trademark of the International Health Terminology Standards Development Organisation, all rights reserved. Implementers of SNOMED CT should review [usage terms](https://www.snomed.org/get-snomed) or directly contact SNOMED International: info@snomed.org</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -387,14 +392,16 @@
       <c r="A15" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -413,7 +420,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -421,30 +428,30 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -463,7 +470,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -471,30 +478,30 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -513,7 +520,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -521,36 +528,36 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T11:48:10+00:00</t>
+    <t>2025-04-16T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,22 +59,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T11:48:51+00:00</t>
+    <t>2025-04-16T12:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:31:30+00:00</t>
+    <t>2025-04-16T12:36:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:36:28+00:00</t>
+    <t>2025-04-16T12:41:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:41:18+00:00</t>
+    <t>2025-04-16T13:08:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t>Property</t>
   </si>
@@ -59,22 +59,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T13:08:49+00:00</t>
+    <t>2025-04-17T08:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>HL7 Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
+    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -90,11 +90,6 @@
   </si>
   <si>
     <t>Copyright</t>
-  </si>
-  <si>
-    <t>*   This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement
-*   The SNOMED International IPS Terminology is distributed by International Health Terminology Standards Development Organisation, trading as SNOMED International, and is subject the terms of the [Creative Commons Attribution 4.0 International Public License](https://creativecommons.org/licenses/by/4.0/). For more information, see [SNOMED IPS Terminology](https://www.snomed.org/snomed-ct/Other-SNOMED-products/international-patient-summary-terminology)
-*   The HL7 International IPS implementation guides incorporate SNOMED CT®, used by permission of the International Health Terminology Standards Development Organisation, trading as SNOMED International. SNOMED CT was originally created by the College of American Pathologists. SNOMED CT is a registered trademark of the International Health Terminology Standards Development Organisation, all rights reserved. Implementers of SNOMED CT should review [usage terms](https://www.snomed.org/get-snomed) or directly contact SNOMED International: info@snomed.org</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -392,16 +387,14 @@
       <c r="A15" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>25</v>
-      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -420,7 +413,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -428,30 +421,30 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -470,7 +463,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -478,30 +471,30 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -520,7 +513,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -528,36 +521,36 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>Property</t>
   </si>
@@ -56,10 +56,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T08:21:49+00:00</t>
+    <t>2025-04-17T08:44:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -327,51 +330,53 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>9</v>
@@ -379,22 +384,22 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -413,38 +418,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -463,38 +468,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -513,44 +518,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T08:44:33+00:00</t>
+    <t>2025-04-17T09:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -125,7 +125,7 @@
     <t>D71</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/sid/icd-10</t>
+    <t>http://hl7.org/fhir/sid/icd-10-cm</t>
   </si>
   <si>
     <t>234532001</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:22:19+00:00</t>
+    <t>2025-04-17T09:39:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:39:14+00:00</t>
+    <t>2025-04-17T11:28:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -62,22 +62,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T11:28:46+00:00</t>
+    <t>2025-04-28T07:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -93,6 +93,11 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>*   This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement
+*   The SNOMED International IPS Terminology is distributed by International Health Terminology Standards Development Organisation, trading as SNOMED International, and is subject the terms of the [Creative Commons Attribution 4.0 International Public License](https://creativecommons.org/licenses/by/4.0/). For more information, see [SNOMED IPS Terminology](https://www.snomed.org/snomed-ct/Other-SNOMED-products/international-patient-summary-terminology)
+*   The HL7 International IPS implementation guides incorporate SNOMED CT®, used by permission of the International Health Terminology Standards Development Organisation, trading as SNOMED International. SNOMED CT was originally created by the College of American Pathologists. SNOMED CT is a registered trademark of the International Health Terminology Standards Development Organisation, all rights reserved. Implementers of SNOMED CT should review [usage terms](https://www.snomed.org/get-snomed) or directly contact SNOMED International: info@snomed.org</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -392,14 +397,16 @@
       <c r="A15" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -418,7 +425,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>23</v>
@@ -426,30 +433,30 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -468,7 +475,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>23</v>
@@ -476,30 +483,30 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -518,7 +525,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>23</v>
@@ -526,36 +533,36 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:30:14+00:00</t>
+    <t>2025-04-28T07:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:30:51+00:00</t>
+    <t>2025-04-28T07:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:00+00:00</t>
+    <t>2025-04-28T07:57:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:33+00:00</t>
+    <t>2025-04-28T07:57:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:44+00:00</t>
+    <t>2025-04-30T14:13:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:13:57+00:00</t>
+    <t>2025-04-30T14:16:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:16:07+00:00</t>
+    <t>2025-04-30T14:16:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:16:39+00:00</t>
+    <t>2025-05-06T09:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T09:47:23+00:00</t>
+    <t>2025-05-06T11:05:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T11:05:16+00:00</t>
+    <t>2025-05-06T11:11:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T11:11:40+00:00</t>
+    <t>2025-05-12T10:14:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -77,7 +77,7 @@
     <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
   </si>
   <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T10:14:30+00:00</t>
+    <t>2025-05-12T19:48:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
   <si>
     <t>Property</t>
   </si>
@@ -29,6 +29,12 @@
     <t>https://www.ehealth.fgov.be/standards/fhir/pss/ValueSet/CompromisedImmuneSystemCodes</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>OID:2.16.840.1.113883.2.51.22.2.48.4</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
@@ -62,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:48:59+00:00</t>
+    <t>2025-05-12T19:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -365,15 +371,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>22</v>
@@ -384,22 +390,22 @@
         <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
         <v>26</v>
       </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -407,6 +413,14 @@
       </c>
       <c r="B16" t="s" s="2">
         <v>28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -425,38 +439,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -475,38 +489,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -525,44 +539,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:50:51+00:00</t>
+    <t>2025-05-12T19:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/sid/icpc2</t>
+    <t>http://hl7.org/fhir/sid/icpc-2</t>
   </si>
   <si>
     <t>D70</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:54:00+00:00</t>
+    <t>2025-05-13T10:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:10+00:00</t>
+    <t>2025-05-13T10:14:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:30+00:00</t>
+    <t>2025-05-13T11:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:53:59+00:00</t>
+    <t>2025-05-13T11:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:54:01+00:00</t>
+    <t>2025-05-13T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:55:17+00:00</t>
+    <t>2025-05-14T06:43:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:43:44+00:00</t>
+    <t>2025-05-14T06:55:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:09+00:00</t>
+    <t>2025-05-14T06:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:38+00:00</t>
+    <t>2025-05-14T06:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:56:25+00:00</t>
+    <t>2025-05-14T07:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:28:26+00:00</t>
+    <t>2025-05-14T07:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:16+00:00</t>
+    <t>2025-05-14T07:30:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:17+00:00</t>
+    <t>2025-05-14T07:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:38:16+00:00</t>
+    <t>2025-05-14T07:51:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:51:32+00:00</t>
+    <t>2025-05-14T07:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:52:33+00:00</t>
+    <t>2025-05-14T07:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:53:22+00:00</t>
+    <t>2025-05-14T08:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:06:44+00:00</t>
+    <t>2025-05-14T08:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:53:34+00:00</t>
+    <t>2025-05-14T08:54:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:54:50+00:00</t>
+    <t>2025-05-14T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:05:29+00:00</t>
+    <t>2025-05-14T13:37:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:37:41+00:00</t>
+    <t>2025-05-14T14:59:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:59:57+00:00</t>
+    <t>2025-05-14T15:00:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:00:45+00:00</t>
+    <t>2025-05-14T15:07:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:07:35+00:00</t>
+    <t>2025-05-14T15:08:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -68,22 +68,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:08:16+00:00</t>
+    <t>2025-05-22T14:06:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -29,12 +29,6 @@
     <t>https://www.ehealth.fgov.be/standards/fhir/pss/ValueSet/CompromisedImmuneSystemCodes</t>
   </si>
   <si>
-    <t>Identifier</t>
-  </si>
-  <si>
-    <t>OID:2.16.840.1.113883.2.51.22.2.48.4</t>
-  </si>
-  <si>
     <t>Version</t>
   </si>
   <si>
@@ -68,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:06:49+00:00</t>
+    <t>2025-05-22T14:43:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -371,15 +365,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>22</v>
@@ -390,22 +384,22 @@
         <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>11</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -413,14 +407,6 @@
       </c>
       <c r="B16" t="s" s="2">
         <v>28</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -439,38 +425,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -489,38 +475,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -539,44 +525,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:43:01+00:00</t>
+    <t>2025-05-22T14:52:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:52:21+00:00</t>
+    <t>2025-06-11T04:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T04:00:37+00:00</t>
+    <t>2025-06-26T13:57:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-26T13:57:34+00:00</t>
+    <t>2025-07-16T16:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T16:47:23+00:00</t>
+    <t>2025-07-16T16:49:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-CompromisedImmuneSystemCodes.xlsx
+++ b/ValueSet-CompromisedImmuneSystemCodes.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
   <si>
     <t>Property</t>
   </si>
@@ -29,6 +29,12 @@
     <t>https://www.ehealth.fgov.be/standards/fhir/pss/ValueSet/CompromisedImmuneSystemCodes</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>OID:2.16.840.1.113883.2.51.22.2.48.4</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
@@ -62,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T16:49:48+00:00</t>
+    <t>2025-07-18T09:14:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -365,15 +371,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>22</v>
@@ -384,22 +390,22 @@
         <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
         <v>26</v>
       </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -407,6 +413,14 @@
       </c>
       <c r="B16" t="s" s="2">
         <v>28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -425,38 +439,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -475,38 +489,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -525,44 +539,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
